--- a/out/policy_events_2026-05-04.xlsx
+++ b/out/policy_events_2026-05-04.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,22 +471,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>"독일, 트럼프 EU산 車·트럭 관세 인상에 26조원 손실 전망" - 뉴스1</t>
+          <t>미군 철수·관세 위협에 獨 "美, 가장 중요한 파트너" 진땀 - 마켓인</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>"독일, 트럼프 EU산 車·트럭 관세 인상에 26조원 손실 전망"&amp;nbsp;&amp;nbsp;뉴스1EU “미, 자동차 보복관세 25% 무역합의 어겨” 대응 경고&amp;nbsp;&amp;nbsp;경향신문靑 ‘美 , EU 車관세 인상’에 “영향 분석해 대응”&amp;nbsp;&amp;nbsp;서울경제</t>
+          <t>미군 철수·관세 위협에 獨 "美, 가장 중요한 파트너" 진땀&amp;nbsp;&amp;nbsp;마켓인</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 07:26:19 GMT</t>
+          <t>Sun, 03 May 2026 22:54:38 GMT</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1KZi1HRnRVMUFKWjNRTF9kZnBFZEt3am5GTC16SkxkbDRwczN0ZGlzNzA0bndOYlVzNlJmTmJYM1J2N2xKel81MTRiRXhfZzdoeVM4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE1WU3c4MExRMDhlWUxMYnc4blpsYWZ4VjczcGVkaUMwQVgxV3hnWll0RjRUNzMtajl6VjlvTnJ1UlNPajcwaU5JR0VfLWp2TTlZemVieFBiSnBnTE1UVFRDTjZXN2MzQ3c5UFZiLWl0U1FOQlU?oc=5</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>獨총리, '미군감축·관세인상' 후폭풍에 "美, 최우선 동맹"(종합) - v.daum.net</t>
+          <t>트럼프 때리더니…독일 총리, ‘주독 미군 철수·車 관세 인상’ 수습 나서 - 매일경제</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>獨총리, '미군감축·관세인상' 후폭풍에 "美, 최우선 동맹"(종합)&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>트럼프 때리더니…독일 총리, ‘주독 미군 철수·車 관세 인상’ 수습 나서&amp;nbsp;&amp;nbsp;매일경제</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 19:02:10 GMT</t>
+          <t>Sun, 03 May 2026 21:51:23 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE1HTV80b2tHdUstbWV0ejNQTzFEVlBjOFRnYlRiV05Ub0VJeG1DZS1OSkRKdy1QeXEwb2hjM1IxMDVLLU0wTlBNNHNpMl9tX2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiUkFVX3lxTE1aZmpVWk05ZEh5YXJsTXJnZFhPQVZDNkZ4eUZQRjlkUHhUdGRTS3d4bUFWajlybVdaTEhvTDlkUHZBWWcwMjBjZUx4S0RRZ0hDdmc?oc=5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -545,22 +545,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>트럼프, 전쟁 안 도왔다고 주독미군 감축·유럽 관세인상…“가장 큰 안보위협은 적 아니라 동맹 붕괴” - 경향신문</t>
+          <t>'미군 감축, 관세 인상' 트럼프 초강수에…독일 총리 사태 수습 - v.daum.net</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>트럼프, 전쟁 안 도왔다고 주독미군 감축·유럽 관세인상…“가장 큰 안보위협은 적 아니라 동맹 붕괴”&amp;nbsp;&amp;nbsp;경향신문</t>
+          <t>'미군 감축, 관세 인상' 트럼프 초강수에…독일 총리 사태 수습&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 04:36:00 GMT</t>
+          <t>Sun, 03 May 2026 22:50:58 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE1uelZybmFqWndHUXdtWW5EVF92YUZ4Q3hUcm9DTXZZbmJseklBeFZialkwZzhOUEJ5blhodUpYUU5CMHNwRmE1WkU4bmZYaVoyZlVkWVZOZ096UdIBX0FVX3lxTE5wV3FROWdKaUJnck84UGtxYTFEWktRZW1mNTFhSEdIU1h0OGN3RG9hY29tblhWc2dYRFlaQ0JRY0RoVW5BelhQd1p6ZDBTQVFLNlg1OHA5TkFNS0tHdUtN?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5uN2xQOXhqeWdGeE02MFhFNEs5MDd5Y1NaZjFnWVVnRzh3VmVKVWFzb2R3YW1NSzlyaGtXQ1pvN2RKNjRhdHRFR1oxRlN2Tkk?oc=5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -656,22 +656,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>FT "美자동차 빅3, 원자재 충격 7조원…관세 타격 맞먹어" - 마켓인</t>
+          <t>[사설]트럼프의 주독미군 감축·EU 관세, 원칙 지키며 대비하길 - 경향신문</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>FT "美자동차 빅3, 원자재 충격 7조원…관세 타격 맞먹어"&amp;nbsp;&amp;nbsp;마켓인</t>
+          <t>[사설]트럼프의 주독미군 감축·EU 관세, 원칙 지키며 대비하길&amp;nbsp;&amp;nbsp;경향신문</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 07:27:13 GMT</t>
+          <t>Sun, 03 May 2026 12:41:00 GMT</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE9ySlIyTkZfUlJFcUt2cklKZGNZUnM1QjliTmNtaGlIaXBhOUNIUmc3RzRPY0NteWpZSHB2T0liRjFsR0J4czhvWXV4MXJfS0FXNWEwLXhwY3VnR1lFNFRTdllxSEtlUnlwcmhjSndDNW1raHc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tYTV3dDNUQjlIWWZtczhJQ3dQeFk2cm1YcmwxVW9vb3pOWU54X0U0Zm1PZGdUNXJJRU5nLWFDS0ZiS1RfTW1rQzl2ZkRHOFQ0UzlaNHhGVEJXZ9IBX0FVX3lxTE45YVUtamFUaXhTcnQ0TTNveVNoeC1Mcjd0cFVVUzUxUGFJa3VQRmdTMVdWNFM0aU1WTENaSzl5OTU2MVRSeWM5WVJ1ZS16Xzd1NlRraDhWVzJueWpvV01N?oc=5</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -693,22 +693,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>이란전 장기화에… 트럼프, 동맹에 노골적 경제 보복, EU에 관세 25% 이어 "이란과 거래 해운사 제재" - 뉴데일리 경제</t>
+          <t>독일, ‘미군 감축·관세인상’ 후폭풍에 “최우선 동맹” - KBS 뉴스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>이란전 장기화에… 트럼프, 동맹에 노골적 경제 보복, EU에 관세 25% 이어 "이란과 거래 해운사 제재"&amp;nbsp;&amp;nbsp;뉴데일리 경제</t>
+          <t>독일, ‘미군 감축·관세인상’ 후폭풍에 “최우선 동맹”&amp;nbsp;&amp;nbsp;KBS 뉴스</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 00:35:06 GMT</t>
+          <t>Sun, 03 May 2026 21:09:00 GMT</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMie0FVX3lxTFBCbS1MWnk4eVRvYXIwc2JvS1NEcDV1dElFOUdiMHhkYmJRUm1manM2aXBLREhpZEc4c0Q1WUhxOGlrd01tVE13TTdlejB4QS1KQ1FoODhHNzJOMFViMFJaM2VUV29YYU1aX0ZTcGRsalRJRzREcEJJMDFfcw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE9mTzY1d3FtMG9aeUxLUTc5bVM5enFPd3RsN3BBdDg3Yy1rU0RTOUZxOHg0LUc0YUZjNXU5dzNFNTZMeVJnaWRUWEs4S0hlSDQtZTIxSFRIVWROeG8?oc=5</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -730,22 +730,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>[사설] 주둔미군 감축· 관세 인상… 美 ‘패키지 보복’ 면밀 대응을 - 서울신문</t>
+          <t>獨, '미군감축·관세 인상' 연타에 트럼프 달래기?…동맹 부각 - 연합뉴스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[사설] 주둔미군 감축· 관세 인상… 美 ‘패키지 보복’ 면밀 대응을&amp;nbsp;&amp;nbsp;서울신문</t>
+          <t>獨, '미군감축·관세 인상' 연타에 트럼프 달래기?…동맹 부각&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 11:44:02 GMT</t>
+          <t>Sun, 03 May 2026 15:34:23 GMT</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxNeHkyOTVBdHVQX1F0OVdXM3JON3ZhNzg2cFJMYnVYOVNWRkJyUzFvSnJYMldNQ3NRNWhKUTZ3S2NXSFhudGpuN3JtNWgyNnlkTnU2NTRnQm5MMUhJZml6WDRTUnhzYzJOT1RZZ29pZjIxbFlSWHQyT2k0c1h2Yk5mSVd3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE5EVU9EVGNOQzVBWjZNMFFTRjVFTWRJdkg4NGg5X1lKaFppZFF1SkZhYjd2OE96UDIxUElSRkdXVDZjWDkwNDVjVWlZb0NxbExDbkpSLWZIdXluR1HSAWBBVV95cUxPLVV2QkUyQm4tOVZVTGQ3cHNYNGFaZmlPekJTSERyd2txS0p3X2ZRbHhfb2FkLURzOTVUejNHcmdFNkRaRmtBaVp4WUloXzRwSldNZDdwMENIeFZBQ0VEMUc?oc=5</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 11:08:00 GMT</t>
+          <t>Sun, 03 May 2026 22:18:00 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -804,22 +804,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>[사설] 미군 감축·관세 폭탄… ‘트럼프 리스크’ 선제 관리해야 - v.daum.net</t>
+          <t>獨총리, '미군감축·관세인상' 후폭풍에 "美, 최우선 동맹"(종합) - 연합뉴스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>[사설] 미군 감축·관세 폭탄… ‘트럼프 리스크’ 선제 관리해야&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>獨총리, '미군감축·관세인상' 후폭풍에 "美, 최우선 동맹"(종합)&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 15:00:00 GMT</t>
+          <t>Sun, 03 May 2026 19:00:40 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9wYnF1S0Q2WS15aGw0cndrNkExcTFaajBKZU1CbEVyVjRTelZOMEVvX0VSdm1NcG02UlBmaXpxX2JCNUF3aFFSMFE5UWtGZlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE10UFlUZDVGZnNrYWNNQl90TnFRcFdOY2NLcE5fb005T1VHT3pfSUw5LTRzSDczWk0tVVR3RkZVZmJJS2lCTFJUMWVzWEZqZEJXMWpJU3Y2TjdmNzDSAWBBVV95cUxNY3ZVSE9ZQmlVN21jVDFLVVhlWEw1YXN5aDFyNkY5YWQ2bnhKdkhxUVc1RXhiTWktZmIxaXMzUWR4dGxtLUYzUGQ3c0gwWElhTXR0cXN1Skt1NnhTTV80QmE?oc=5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -841,22 +841,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>트럼프 “관세 25% 인상” 발표에···EU “합의 위반시 대응 조치” - 경향신문</t>
+          <t>이란 전쟁에...美 자동차 빅3, 원자재 충격 관세 타격 맞먹어 - v.daum.net</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>트럼프 “관세 25% 인상” 발표에···EU “합의 위반시 대응 조치”&amp;nbsp;&amp;nbsp;경향신문</t>
+          <t>이란 전쟁에...美 자동차 빅3, 원자재 충격 관세 타격 맞먹어&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 08:40:00 GMT</t>
+          <t>Sun, 03 May 2026 19:48:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5lWXRzcVVfOE1qWnFZTUdETXhNVnJjLXFDTmxpNVppQ0VMV2VFbU1QYnQwYnNLbU9sd2MwX3JFcG5TaW9CeUZUbldkb213YTNIejduVFVRTnJNd9IBX0FVX3lxTE5KVE1VRV9BZnZsN055b3JfRU1TZ1d0NER4R1ZvenZ1emk2RW1sdmE4cHFXX1dPekp0bDJDTWZsVG9CRzdiNGdOc2VzWmc2aFAybGs2bUE3UDVRcmlfUUs4?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFB0blZXMFJuWTlKWVdPY0M3WWdvZmgxQnFxREQ5VmNuNlFXcTRBVWVjSnVFbGxYXzRWV3liVnhzWWlqRlpTbmJ4akpQbVBaMkE?oc=5</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -878,22 +878,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>‘이란戰 뒤끝’ 동맹과의 관세 전쟁 재개한 트럼프…한국 영향은? - 동아일보</t>
+          <t>독일, ‘미군 감축·관세 인상’ 연타에…“미국은 가장 중요한 동맹” - 중앙일보</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>‘이란戰 뒤끝’ 동맹과의 관세 전쟁 재개한 트럼프…한국 영향은?&amp;nbsp;&amp;nbsp;동아일보</t>
+          <t>독일, ‘미군 감축·관세 인상’ 연타에…“미국은 가장 중요한 동맹”&amp;nbsp;&amp;nbsp;중앙일보</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 10:57:00 GMT</t>
+          <t>Sun, 03 May 2026 20:33:02 GMT</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBhSVc2Vkh2bWdvQUkwQ2RjVmRVampMRzhQaElya09pdU1Qc1JPMWFaM0swSFg0ckxFQ1NKcC1CNnZiVk50WlplRERnbjMwc0JzWGM3NFo0cFlKaEFBWWNhVU95bkROMy04dGFtZGU4MlA3OG_SAWZBVV95cUxQRmZsaGk1azFPTU9xMVdzamlLY2FNenBZcDBVUUM2Zk1Hbk9aNXcwUUwyR21tblNkbERKV2NPcVNhX0pZdmNkV1Q5VmtKOW4xclNMYk5pSnotMHlwZUxpd05HenVWVVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE1mblFBZDJxR0h5Um1lNlpTdm92ZnMyeG5JQTIxQXpScTRHNkFDWjVfLWE1SnVubWU3V0M3Ni1zZjIzTVU0NmtPal83QUtRblFyajl5Sk53?oc=5</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -903,7 +903,7 @@
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" t="inlineStr"/>
     </row>
@@ -915,22 +915,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>트럼프, 유럽에 '이란전 뒤끝'?…주독미군 감축, 자동차 관세 인상까지 - 프레시안</t>
+          <t>트럼프 “EU 車에 25% 관세”… 獨 52조 손실 전망 - 동아일보</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>트럼프, 유럽에 '이란전 뒤끝'?…주독미군 감축, 자동차 관세 인상까지&amp;nbsp;&amp;nbsp;프레시안</t>
+          <t>트럼프 “EU 車에 25% 관세”… 獨 52조 손실 전망&amp;nbsp;&amp;nbsp;동아일보</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 09:02:50 GMT</t>
+          <t>Sun, 03 May 2026 19:30:00 GMT</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE8xbGNFOXBkY3VZMWpkWUpRaFd2azJTN2k0a1pQNkpWSldnS2NYRE5kcVFBSEg2SmtNclNxVm1OLUZwWVFBUXk4QnBHMnpwbFhnYktKVF9xVjQ0S212SFNyWDhpOVU5eU5sOGhF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTFBiTkdjZXc3bkE2bHJUdlVEZjNGTDNVNE9OV1RoLVhlbHI0S2N4ODMzUWRWNU1BTXI0dGduSllvYWZndFZXU2VOYU15bFVCR3dILVFadnVxOWxma29ZbGIteGJDMWF0a3FHLWQ1RWRVZ0VCbmPSAWZBVV95cUxQQ0FzQ1lENFUwM2hic2hETm50MTFzQm9wdkt0N1BMTklWUVhJV3FWbTRoaTN1Tml1R09TMTVHREhBN1RDN18tVk95Wmhuall4ZkVNanltNGdraDU3OHBIYXpITEhJNnc?oc=5</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -952,22 +952,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>“미국 車관세 25％로 올리면 독일 26조원 손실” - 헬로티</t>
+          <t>‘제로 관세’로 중국-아프리카 협력의 케이크를 키운다 - 현장언론 민플러스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>“미국 車관세 25％로 올리면 독일 26조원 손실”&amp;nbsp;&amp;nbsp;헬로티</t>
+          <t>‘제로 관세’로 중국-아프리카 협력의 케이크를 키운다&amp;nbsp;&amp;nbsp;현장언론 민플러스</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Sat, 02 May 2026 22:30:00 GMT</t>
+          <t>Sun, 03 May 2026 23:26:03 GMT</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiX0FVX3lxTFBDUEhXZWdUU0tlMHVJWF93VVU4SF85c3YwTFZnT1cyVTJUSUtHUGo3aE82NmtrYmlCbkYzVDZ5YllLZzBSTG9qUmxqczU1VlZ3WnhVbXBCYnA1RFpQbXhV?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFBVb3BnS3c1Q2ZtX2xvN0RjMG5oV2NnVW5qWUYySjJqUzczU3pQTm5fdjkxMW0yUVdKcHJEZXhsMkdHZGVoZ1pqSjA0dGktNV9sMldBV2lXSFNSUEU2VlZUV1ZVaVQ4bERIZkUtcnRn?oc=5</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I15" t="inlineStr"/>
     </row>
@@ -989,22 +989,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>中, 아프리카 53개 수교국 대상 제로 관세 조치 전면 발효 - 인민망 한국어판</t>
+          <t>트럼프 “관세 25% 인상” 발표에···EU “합의 위반시 대응 조치” - 경향신문</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>中, 아프리카 53개 수교국 대상 제로 관세 조치 전면 발효&amp;nbsp;&amp;nbsp;인민망 한국어판</t>
+          <t>트럼프 “관세 25% 인상” 발표에···EU “합의 위반시 대응 조치”&amp;nbsp;&amp;nbsp;경향신문</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 03:18:00 GMT</t>
+          <t>Sun, 03 May 2026 08:40:00 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTFB6bXJJR1ZfNFRwVHFZYThfSjlEd3Zmams0OEdDQ2pGMVpJclJEQm5SSVhuWkZfUlQyVFBkaFp3NlExTWUwX2xMSFBuNjdVQ1VERWJ4cEJncG8wcGhQTVFyTllobmxRc01xa0Nr?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5lWXRzcVVfOE1qWnFZTUdETXhNVnJjLXFDTmxpNVppQ0VMV2VFbU1QYnQwYnNLbU9sd2MwX3JFcG5TaW9CeUZUbldkb213YTNIejduVFVRTnJNd9IBX0FVX3lxTE5KVE1VRV9BZnZsN055b3JfRU1TZ1d0NER4R1ZvenZ1emk2RW1sdmE4cHFXX1dPekp0bDJDTWZsVG9CRzdiNGdOc2VzWmc2aFAybGs2bUE3UDVRcmlfUUs4?oc=5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1014,7 +1014,7 @@
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr"/>
     </row>
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>‘독일 때리는’ 트럼프 “미군 5천명보다 많이 철수…자동차 관세 인상” - 한겨레</t>
+          <t>독일 총리, ‘미군감축·관세인상’ 후폭풍에 “미국, 최우선 동맹” - KBS 뉴스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>‘독일 때리는’ 트럼프 “미군 5천명보다 많이 철수…자동차 관세 인상”&amp;nbsp;&amp;nbsp;한겨레</t>
+          <t>독일 총리, ‘미군감축·관세인상’ 후폭풍에 “미국, 최우선 동맹”&amp;nbsp;&amp;nbsp;KBS 뉴스</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 11:18:00 GMT</t>
+          <t>Sun, 03 May 2026 19:31:00 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFAtRmZaNlZPcDZmY05CQktsWXVxU29mUlVOUlVqckt0aXhSRWw1akZTN2k4amlYMThueUNOTi14TVBFeFZjbXlFVTlXbTFoMWZlVE9FRV9SVEdjODRYQ3k5UTBLNGpZY2lreUxzQmhSRQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE96R0lFOXBkTkhva19IQ09vN09tUHp6Qmp1TmRvSHdUM3E2U2dSVDFGbmZwM1BtaEtrNnNDa0NVbTA5QVM0bEpJQUJVLW9BZEg5VXpWcVVXZjdKVTQ?oc=5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1063,22 +1063,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>트럼프의 뒤끝 "EU産 차관세 25%로 인상"… 이란전 비협조 보복 - v.daum.net</t>
+          <t>주독미군 15% 감축·유럽 차 25% 관세… 동맹에 보복 나선 트럼프 - 서울신문</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>트럼프의 뒤끝 "EU産 차관세 25%로 인상"… 이란전 비협조 보복&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>주독미군 15% 감축·유럽 차 25% 관세… 동맹에 보복 나선 트럼프&amp;nbsp;&amp;nbsp;서울신문</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 08:45:04 GMT</t>
+          <t>Sun, 03 May 2026 15:26:24 GMT</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9Tcmk2cE1VbDNVQXNDd3NncWRpU0NPY1duTDFhZy1ZQlVXaDdFS2NhT2phSHZyMXhocHhVMnBNRkROZzVUTXlYeklNNVdKdU0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE8tMGdOY0VCN2lVTGN5WG9zb0lwWExnMnhSQnRQd1EyZzA1WTdJdzNYSThieV8tZG16cDlJVmhacDFGWmRBZVJieENZd0tlMmZWSjY0N29mR01iMVhvS1VESS1DQ2E2YnpEWGwzczFtUk9LWTVKcFFJ?oc=5</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1100,22 +1100,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[사설] 미 유럽에 병력 감축·관세 ‘보복’, 우리도 대비해야 - 한겨레</t>
+          <t>獨총리 “美, 최우선 동맹” 미군 감축·관세 갈등 사태 수습 - 헤럴드경제</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[사설] 미 유럽에 병력 감축·관세 ‘보복’, 우리도 대비해야&amp;nbsp;&amp;nbsp;한겨레</t>
+          <t>獨총리 “美, 최우선 동맹” 미군 감축·관세 갈등 사태 수습&amp;nbsp;&amp;nbsp;헤럴드경제</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 12:37:00 GMT</t>
+          <t>Sun, 03 May 2026 20:56:55 GMT</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1iMlBCdWpRMVoyakRKWDVvMnA2cFhDWC1WcVc2dFVkOHVxTkpEWDkxZjQ4ZWxvWWhUVmZwVGlZRWZhUkhYWGVIc25UQWlzTjllTUY3NE9WQktrWmJ4VkgzNHh3ZnljZGZVa0E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiVkFVX3lxTE9NcUJYUEs0a0ZsTkdUSG15Tmh5Tm9NbzFBSWVPenZySFRBMGRVNzhkbFFEcWNFWm1wZlFybFNfYWpDNjhmbU5yX3J2THJYS2RXTkxOYWxn?oc=5</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1137,22 +1137,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>[사설] 주독미군 감축·EU 관세 압박… 한국도 대비 서둘러야 - v.daum.net</t>
+          <t>‘독일 때리는’ 트럼프 “미군 5천명보다 많이 철수…자동차 관세 인상” - 한겨레</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[사설] 주독미군 감축·EU 관세 압박… 한국도 대비 서둘러야&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>‘독일 때리는’ 트럼프 “미군 5천명보다 많이 철수…자동차 관세 인상”&amp;nbsp;&amp;nbsp;한겨레</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 16:23:02 GMT</t>
+          <t>Sun, 03 May 2026 11:18:00 GMT</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE54U2NOVjJJV3lNTkI2M0JuWl9BcUNJN0lMSzFuVExMakgtelBwN3BhTV9JbjB0eFAya1Vac1p3dlQwaGF5YkhrYTNOSmctVHM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFAtRmZaNlZPcDZmY05CQktsWXVxU29mUlVOUlVqckt0aXhSRWw1akZTN2k4amlYMThueUNOTi14TVBFeFZjbXlFVTlXbTFoMWZlVE9FRV9SVEdjODRYQ3k5UTBLNGpZY2lreUxzQmhSRQ?oc=5</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I20" t="inlineStr"/>
     </row>
@@ -1174,22 +1174,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>[사설]트럼프의 주독미군 감축·EU 관세, 원칙 지키며 대비하길 - 경향신문</t>
+          <t>[사설] 미군 감축·관세 폭탄… ‘트럼프 리스크’ 선제 관리해야 - v.daum.net</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[사설]트럼프의 주독미군 감축·EU 관세, 원칙 지키며 대비하길&amp;nbsp;&amp;nbsp;경향신문</t>
+          <t>[사설] 미군 감축·관세 폭탄… ‘트럼프 리스크’ 선제 관리해야&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 12:41:00 GMT</t>
+          <t>Sun, 03 May 2026 15:00:00 GMT</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTE5tYTV3dDNUQjlIWWZtczhJQ3dQeFk2cm1YcmwxVW9vb3pOWU54X0U0Zm1PZGdUNXJJRU5nLWFDS0ZiS1RfTW1rQzl2ZkRHOFQ0UzlaNHhGVEJXZ9IBX0FVX3lxTE45YVUtamFUaXhTcnQ0TTNveVNoeC1Mcjd0cFVVUzUxUGFJa3VQRmdTMVdWNFM0aU1WTENaSzl5OTU2MVRSeWM5WVJ1ZS16Xzd1NlRraDhWVzJueWpvV01N?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9wYnF1S0Q2WS15aGw0cndrNkExcTFaajBKZU1CbEVyVjRTelZOMEVvX0VSdm1NcG02UlBmaXpxX2JCNUF3aFFSMFE5UWtGZlE?oc=5</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1211,22 +1211,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>대서양동맹 갈등…일부 미군 철수·車관세 인상, 韓도 예의주시 - v.daum.net</t>
+          <t>[사설] 미 유럽에 병력 감축·관세 ‘보복’, 우리도 대비해야 - 한겨레</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>대서양동맹 갈등…일부 미군 철수·車관세 인상, 韓도 예의주시&amp;nbsp;&amp;nbsp;v.daum.net</t>
+          <t>[사설] 미 유럽에 병력 감축·관세 ‘보복’, 우리도 대비해야&amp;nbsp;&amp;nbsp;한겨레</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 05:45:47 GMT</t>
+          <t>Sun, 03 May 2026 12:37:00 GMT</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5kaXhZWlJaVko3cHk0c0RyU2IxTVlzMVVZVHQ0M2tkcXJaaDdrdXZhenJoakJWT1F6bjEyc3Z4d0FWeURFYzhIVERVakJTLVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1iMlBCdWpRMVoyakRKWDVvMnA2cFhDWC1WcVc2dFVkOHVxTkpEWDkxZjQ4ZWxvWWhUVmZwVGlZRWZhUkhYWGVIc25UQWlzTjllTUY3NE9WQktrWmJ4VkgzNHh3ZnljZGZVa0E?oc=5</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1243,27 +1243,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>FTA</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中 랜드브리지, 호주 다윈항 국유화 추진에 국제소송…“안보 명분 계약 파기, FTA 위반” 반격 - 해사신문</t>
+          <t>독일, ‘미군 감축·관세인상’ 후폭풍에 “최우선 동맹” - v.daum.net</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>中 랜드브리지, 호주 다윈항 국유화 추진에 국제소송…“안보 명분 계약 파기, FTA 위반” 반격&amp;nbsp;&amp;nbsp;해사신문</t>
+          <t>독일, ‘미군 감축·관세인상’ 후폭풍에 “최우선 동맹”&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 05:54:01 GMT</t>
+          <t>Sun, 03 May 2026 21:22:35 GMT</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE0xcVozX0ZGZHctbFdRR1dHX0ZaeGlWM213ZjEwUGEyMlFuaXg1ZW9nRG1Ic19QWm9zbE4tODFWbGV1WkVQdTdEdDBvVkE2V2NvckNTVXV2RXFKTFpRa0NNdlUyVGJNNVFoQmRn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE5mMUNOVVVJVTZIWENkNFA2dm1xejFSQTY1dUJubUZadlVfNVR4RktabF9qNVVrUHAzSzZXTEdZRVdVejlCdFFnSnRWUmRyTTg?oc=5</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1273,34 +1273,34 @@
       </c>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[기상속보]오늘날씨 출근길 곳곳 비 강원산지 1∼3㎝ 눈 일교차 주의 서울 낮 20도...주말,주간 예보 - 퍼블릭타임스</t>
+          <t>트럼프의 뒤끝 "EU産 차관세 25%로 인상"… 이란전 비협조 보복 - v.daum.net</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[기상속보]오늘날씨 출근길 곳곳 비 강원산지 1∼3㎝ 눈 일교차 주의 서울 낮 20도...주말,주간 예보&amp;nbsp;&amp;nbsp;퍼블릭타임스</t>
+          <t>트럼프의 뒤끝 "EU産 차관세 25%로 인상"… 이란전 비협조 보복&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 20:00:00 GMT</t>
+          <t>Sun, 03 May 2026 08:45:04 GMT</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5uOTZBRHY3aE5vRHN5ZkNUcWJuMWlxMS0tTWlrOXlMb0NkRXp3NUYzbkpFUEJmbjBodXJXRk9aZFh3ejdzRWFCYnZhUUVDOFBhRVNmY2R3V1d4M0xlZV9WR25uZVdEcXhDVnfSAW5BVV95cUxOR0V0UHByTEhUTENWdWhhMGdKRTVMMDNZdUJmb2pub01sQjdjNGdQQTJuZ1U4VDFFWVA0NEF5bkxUS1Rqa2dEOGIyN1p2TVl4VFJUSmYzdWN6a3E4ZUhkSXFKVnJNOG1XUFF2ekNCUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTE9Tcmk2cE1VbDNVQXNDd3NncWRpU0NPY1duTDFhZy1ZQlVXaDdFS2NhT2phSHZyMXhocHhVMnBNRkROZzVUTXlYeklNNVdKdU0?oc=5</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1310,34 +1310,34 @@
       </c>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>[내일날씨] 출근길 '비' 오후에 차차 맑아져⋯강원산지 '눈' 올 수도 - 아이뉴스24</t>
+          <t>트럼프, 유럽에 '이란전 뒤끝'?…주독미군 감축, 자동차 관세 인상까지 - 프레시안</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>[내일날씨] 출근길 '비' 오후에 차차 맑아져⋯강원산지 '눈' 올 수도&amp;nbsp;&amp;nbsp;아이뉴스24</t>
+          <t>트럼프, 유럽에 '이란전 뒤끝'?…주독미군 감축, 자동차 관세 인상까지&amp;nbsp;&amp;nbsp;프레시안</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 10:59:33 GMT</t>
+          <t>Sun, 03 May 2026 09:02:50 GMT</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE8yeEllY2lfTGNjbk1SQ3FtUlJEMkFGaGFIcjlPQzJiMHJBSWtwcTgxYTI5dUgtbWJocXNqM2JkNnB5QWp5VUhKb2xPdmY?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE8xbGNFOXBkY3VZMWpkWUpRaFd2azJTN2k0a1pQNkpWSldnS2NYRE5kcVFBSEg2SmtNclNxVm1OLUZwWVFBUXk4QnBHMnpwbFhnYktKVF9xVjQ0S212SFNyWDhpOVU5eU5sOGhF?oc=5</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1347,34 +1347,34 @@
       </c>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>관세</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>마트 바나나 원산지 보니 에콰도르 아니면 필리핀 - thecommoditiesnews.com</t>
+          <t>주간 모빌리티 뉴스: 관세 환급 호재, 포드의 호실적, GM의 제미나이 도입 - Benzinga</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>마트 바나나 원산지 보니 에콰도르 아니면 필리핀&amp;nbsp;&amp;nbsp;thecommoditiesnews.com</t>
+          <t>주간 모빌리티 뉴스: 관세 환급 호재, 포드의 호실적, GM의 제미나이 도입&amp;nbsp;&amp;nbsp;Benzinga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 05:36:18 GMT</t>
+          <t>Sun, 03 May 2026 22:55:41 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9tcjhjanl5ODlpN3ExN0ttTGtDZGtvWS1YUmtZbWREQUlDTmhodjctY0RvUEZmUjhfX2tBLU04anR2VzVabC1yNk53TjJaTlFqT3RwTUgxRVNDYXMyQ2k4Nk14dGxXY2xTMDQyRmhaQnNXbERiRzFn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi2AJBVV95cUxQUG1OaF9nWmNYWWc3VXMxdHMtd2d1a0x6eHh4OEV3NUw4Wk1TQ1p5SHloRmJFTHVCczA2OWhJQ3l1dDU1cXNEanEtaHFGMmdDa2VPaThvR3kydk5UMm90UHhfekNtTkRBMEFOTmtXSThQQjdUTmJOcmI1VFVvQlNJWEZWdjJOb29MV1JqcF91X0Y5cWxnb2tPczdQMC1BbWJQRGlSeVoxXzFRM0dnNU5FNzdEb1NsZGgydkNOYmhwVG1qb2g0TDBuVk5Ud1l0T2VxNUxyeTJsam1CcEdQTk9BeVY0cWVmbkJIRTZ6WFRLVU9GV3IxdWdXbmYzVU95dERBOE9RTXBzVC12ekQ3NFpnSThwUUQtU0hFUi1VR3VxdGlOTEJHU0piTUlpZl9VUm0yd09UVkwwV3U1QzUzQU96X3U0b2JzQVl6SUdTNms5bUhYU3owd3lMYg?oc=5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1384,34 +1384,34 @@
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>원산지</t>
+          <t>FTA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>[속보] 월요일인 4일 오전까지 중부·호남 비…강원산지엔 ‘눈’ 올 수도 - dt.co.kr</t>
+          <t>中 랜드브리지, 호주 다윈항 국유화 추진에 국제소송…“안보 명분 계약 파기, FTA 위반” 반격 - 해사신문</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>[속보] 월요일인 4일 오전까지 중부·호남 비…강원산지엔 ‘눈’ 올 수도&amp;nbsp;&amp;nbsp;dt.co.kr</t>
+          <t>中 랜드브리지, 호주 다윈항 국유화 추진에 국제소송…“안보 명분 계약 파기, FTA 위반” 반격&amp;nbsp;&amp;nbsp;해사신문</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 08:34:45 GMT</t>
+          <t>Sun, 03 May 2026 05:54:01 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5kQ0NJcjkwbEVCWkp5eUlldGF5QWtMNWxsMEl3ZGU2QU1WUUNLTEV3WEhRWGxxVndEbjM3UGlZZ0xIbHdQOGlvcEtOVm1IUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMia0FVX3lxTE0xcVozX0ZGZHctbFdRR1dHX0ZaeGlWM213ZjEwUGEyMlFuaXg1ZW9nRG1Ic19QWm9zbE4tODFWbGV1WkVQdTdEdDBvVkE2V2NvckNTVXV2RXFKTFpRa0NNdlUyVGJNNVFoQmRn?oc=5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1433,22 +1433,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>어버이날 카네이션, 국산인 줄 알았는데 수입산?…경기농관원 ‘특별 단속’ - 경기일보</t>
+          <t>강원·충북·경북 오전까지 비…강원산지 1㎝ 안팎 눈 - 연합뉴스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>어버이날 카네이션, 국산인 줄 알았는데 수입산?…경기농관원 ‘특별 단속’&amp;nbsp;&amp;nbsp;경기일보</t>
+          <t>강원·충북·경북 오전까지 비…강원산지 1㎝ 안팎 눈&amp;nbsp;&amp;nbsp;연합뉴스</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 06:20:00 GMT</t>
+          <t>Sun, 03 May 2026 20:21:24 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBfVnA4Mnlpd2tPaDU3N2FnTF9kaW5oS0xQTHkxRTBqSjFUbU1zeC1ZdmRlVUJjZHk3T1JjWGROQTZnenlhcFFXZ05lQkZFbDZGaTFJTk5lb1U5OTg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTE05MTFzSVgzdDJjbFJJMXdISHZOVzJuSF9RZmRqaWNCUkdfZDFheDF6cmtVQXVxdFdFY3ZDQW5KZXdHaFp1cG8tc2NERU5pT2stYWJmcjc4M0NwWknSAWBBVV95cUxNYXg4RW0tUEwzZlJpQUQzRG1LOXIzTkNpcHlVRGw3aG9Na3hVVTZQeWlsU0RJS2MwbXdPRFBiR3F3WklVeXFQYWhGbE1qRkZWalh4MEhrSmhEMmhEY2dweFg?oc=5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I28" t="inlineStr"/>
     </row>
@@ -1470,22 +1470,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>날씨, 월요일 전국 '강풍주의보' 강원산지 5cm 눈, 서울날씨는 - gukjenews.com</t>
+          <t>‘망 이용대가’, ‘쿠팡 총수’, ‘식품 원산지 표기 방식’ - 뉴스톱</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>날씨, 월요일 전국 '강풍주의보' 강원산지 5cm 눈, 서울날씨는&amp;nbsp;&amp;nbsp;gukjenews.com</t>
+          <t>‘망 이용대가’, ‘쿠팡 총수’, ‘식품 원산지 표기 방식’&amp;nbsp;&amp;nbsp;뉴스톱</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 19:07:00 GMT</t>
+          <t>Sun, 03 May 2026 20:47:15 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFA4UUN5QktYOFQtUWtpTDNnN1gxczM0YWZHWnBYU0daLXA5Z0pLMHdiUURPZG1lazRib1BYVmp4bGlDTjc3RG5sQWVDZ1dMeFJCVmxDVGtyNGhTWmJnVGR2UC1RdklTUkNFV2J6N1ZB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMib0FVX3lxTFBqT1k0S1RCN2J4Yi0wV2hjZHVhMzZOWDBsWF9DUDhTdFh6ZGx0QkJOX3ZRRVNlZGdWMlRIdUNJajBQWGRIVWE5ZE9XUUxfbmpuN3lYN0hiWEg3TGxDSkhxcWFOZzU4UFpEY2VlZk9IOA?oc=5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1507,22 +1507,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>남양주시, 화훼류 원산지표시 지도·점검 - 경기도민일보 미디어</t>
+          <t>강원·충북·경북 오전까지 비…강원산지 1㎝ 안팎 눈 - v.daum.net</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>남양주시, 화훼류 원산지표시 지도·점검&amp;nbsp;&amp;nbsp;경기도민일보 미디어</t>
+          <t>강원·충북·경북 오전까지 비…강원산지 1㎝ 안팎 눈&amp;nbsp;&amp;nbsp;v.daum.net</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 02:31:01 GMT</t>
+          <t>Sun, 03 May 2026 20:30:05 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjY3VPS2t2Zi1acldERXBGZmRGMi1NR0s1UWdJaGdja3VlZ1ZZa1g0UEpDYnU3cDBHd3NucVZaclBVd1pySi03LUtBLW1GNmJTbGJ4UTR1LURuc0ZRUTk3eGlRUXNLWkFLM3c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiT0FVX3lxTFBpREctZ3VLRmZFaFZMX1NRSFVla0JmX1ZtS1I4LXBsaVRsX0k3MUFCUTJvdDZCSVNOV3pFNHdzendzWE5HNUdFTkZ4dGtaM0U?oc=5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1544,22 +1544,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>월요일 오전까지 중부·호남 비…강원산지에 '눈' 올 수도 - 네이트</t>
+          <t>[내일날씨] 출근길 '비' 오후에 차차 맑아져⋯강원산지 '눈' 올 수도 - 아이뉴스24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>월요일 오전까지 중부·호남 비…강원산지에 '눈' 올 수도&amp;nbsp;&amp;nbsp;네이트</t>
+          <t>[내일날씨] 출근길 '비' 오후에 차차 맑아져⋯강원산지 '눈' 올 수도&amp;nbsp;&amp;nbsp;아이뉴스24</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Sun, 03 May 2026 08:29:00 GMT</t>
+          <t>Sun, 03 May 2026 10:59:33 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1jWmNuMmd1TjZ2NDU2QVlQSmtEbC1LTndQS3k5ZmN2dTZmZU02OUVaN3dtcDNVQ1NSR09tMnlsSHJvZ29idW9NQUJSdVQ3bGMxUml3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiTEFVX3lxTE8yeEllY2lfTGNjbk1SQ3FtUlJEMkFGaGFIcjlPQzJiMHJBSWtwcTgxYTI5dUgtbWJocXNqM2JkNnB5QWp5VUhKb2xPdmY?oc=5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1572,6 +1572,376 @@
         <v>4</v>
       </c>
       <c r="I31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>[기상속보]오늘날씨 출근길 곳곳 비 강원산지 1∼3㎝ 눈 일교차 주의 서울 낮 20도...주말,주간 예보 - 퍼블릭타임스</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[기상속보]오늘날씨 출근길 곳곳 비 강원산지 1∼3㎝ 눈 일교차 주의 서울 낮 20도...주말,주간 예보&amp;nbsp;&amp;nbsp;퍼블릭타임스</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 20:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5uOTZBRHY3aE5vRHN5ZkNUcWJuMWlxMS0tTWlrOXlMb0NkRXp3NUYzbkpFUEJmbjBodXJXRk9aZFh3ejdzRWFCYnZhUUVDOFBhRVNmY2R3V1d4M0xlZV9WR25uZVdEcXhDVnfSAW5BVV95cUxOR0V0UHByTEhUTENWdWhhMGdKRTVMMDNZdUJmb2pub01sQjdjNGdQQTJuZ1U4VDFFWVA0NEF5bkxUS1Rqa2dEOGIyN1p2TVl4VFJUSmYzdWN6a3E4ZUhkSXFKVnJNOG1XUFF2ekNCUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="n">
+        <v>4</v>
+      </c>
+      <c r="I32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>마트 바나나 원산지 보니 에콰도르 아니면 필리핀 - thecommoditiesnews.com</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>마트 바나나 원산지 보니 에콰도르 아니면 필리핀&amp;nbsp;&amp;nbsp;thecommoditiesnews.com</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 05:36:18 GMT</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMid0FVX3lxTE9tcjhjanl5ODlpN3ExN0ttTGtDZGtvWS1YUmtZbWREQUlDTmhodjctY0RvUEZmUjhfX2tBLU04anR2VzVabC1yNk53TjJaTlFqT3RwTUgxRVNDYXMyQ2k4Nk14dGxXY2xTMDQyRmhaQnNXbERiRzFn?oc=5</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="n">
+        <v>4</v>
+      </c>
+      <c r="I33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>[속보] 월요일인 4일 오전까지 중부·호남 비…강원산지엔 ‘눈’ 올 수도 - dt.co.kr</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[속보] 월요일인 4일 오전까지 중부·호남 비…강원산지엔 ‘눈’ 올 수도&amp;nbsp;&amp;nbsp;dt.co.kr</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 08:34:45 GMT</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiTkFVX3lxTE5kQ0NJcjkwbEVCWkp5eUlldGF5QWtMNWxsMEl3ZGU2QU1WUUNLTEV3WEhRWGxxVndEbjM3UGlZZ0xIbHdQOGlvcEtOVm1IUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="n">
+        <v>4</v>
+      </c>
+      <c r="I34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>날씨, 월요일 전국 '강풍주의보' 강원산지 5cm 눈, 서울날씨는 - gukjenews.com</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>날씨, 월요일 전국 '강풍주의보' 강원산지 5cm 눈, 서울날씨는&amp;nbsp;&amp;nbsp;gukjenews.com</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 19:07:00 GMT</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTFA4UUN5QktYOFQtUWtpTDNnN1gxczM0YWZHWnBYU0daLXA5Z0pLMHdiUURPZG1lazRib1BYVmp4bGlDTjc3RG5sQWVDZ1dMeFJCVmxDVGtyNGhTWmJnVGR2UC1RdklTUkNFV2J6N1ZB?oc=5</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="n">
+        <v>4</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>어버이날 카네이션, 국산인 줄 알았는데 수입산?…경기농관원 ‘특별 단속’ - 경기일보</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>어버이날 카네이션, 국산인 줄 알았는데 수입산?…경기농관원 ‘특별 단속’&amp;nbsp;&amp;nbsp;경기일보</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 06:20:00 GMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiW0FVX3lxTFBfVnA4Mnlpd2tPaDU3N2FnTF9kaW5oS0xQTHkxRTBqSjFUbU1zeC1ZdmRlVUJjZHk3T1JjWGROQTZnenlhcFFXZ05lQkZFbDZGaTFJTk5lb1U5OTg?oc=5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>월요일 오전까지 중부·호남 비…강원산지에 '눈' 올 수도 - 네이트</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>월요일 오전까지 중부·호남 비…강원산지에 '눈' 올 수도&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 08:29:00 GMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE1jWmNuMmd1TjZ2NDU2QVlQSmtEbC1LTndQS3k5ZmN2dTZmZU02OUVaN3dtcDNVQ1NSR09tMnlsSHJvZ29idW9NQUJSdVQ3bGMxUml3?oc=5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>4</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>원산지</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>남양주시, 화훼류 원산지표시 지도·점검 - 경기도민일보 미디어</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>남양주시, 화훼류 원산지표시 지도·점검&amp;nbsp;&amp;nbsp;경기도민일보 미디어</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 02:31:01 GMT</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBjY3VPS2t2Zi1acldERXBGZmRGMi1NR0s1UWdJaGdja3VlZ1ZZa1g0UEpDYnU3cDBHd3NucVZaclBVd1pySi03LUtBLW1GNmJTbGJ4UTR1LURuc0ZRUTk3eGlRUXNLWkFLM3c?oc=5</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="n">
+        <v>4</v>
+      </c>
+      <c r="I38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>무역구제</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>산업부, 파키스탄과 CEPA 체결 위한 첫 공식협상 개최 - 뉴시스</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>산업부, 파키스탄과 CEPA 체결 위한 첫 공식협상 개최&amp;nbsp;&amp;nbsp;뉴시스</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBNOFE4blBWY3VMTWdBT0phUVQwN2s2aGdMMy1fTG5ua1l1TDc5TVVvU1VTbkdQalc2OXJ0Y05jMnVmX2JjUkh1T3VGQVd1V2JFMlBYdU1qNnZtWnV0MVB2cExIcnZfQVpLNERrUnRINWZJSWhXaXZRZ9IBeEFVX3lxTFBNOFE4blBWY3VMTWdBT0phUVQwN2s2aGdMMy1fTG5ua1l1TDc5TVVvU1VTbkdQalc2OXJ0Y05jMnVmX2JjUkh1T3VGQVd1V2JFMlBYdU1qNnZtWnV0MVB2cExIcnZfQVpLNERrUnRINWZJSWhXaXZRZw?oc=5</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>무역구제</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>한-파키스탄 CEPA 1차 공식협상, 7일까지 개최…경제협력·투자 논의 - 뉴스1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>한-파키스탄 CEPA 1차 공식협상, 7일까지 개최…경제협력·투자 논의&amp;nbsp;&amp;nbsp;뉴스1</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 21:00:00 GMT</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE5hSDJMYnVmTWtYWk1idkhlR1o2SVd0RUlObF84UVhHbDUtNWhuNUZDUy1NUE5qZC1JTjh3aXMyaFZFb1Z6VkpZWk5HT3pWeE1lYnRZSVF3RkdqbzFF?oc=5</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>무역구제</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>서남아 수출 다변화 시동···한-파키스탄 CEPA 첫 공식협상 - 네이트</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>서남아 수출 다변화 시동···한-파키스탄 CEPA 첫 공식협상&amp;nbsp;&amp;nbsp;네이트</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sun, 03 May 2026 22:47:00 GMT</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiU0FVX3lxTE0tQmdDTGJjOVhKWkFjTjJPb2xvRnQ4WlZXV09yWTVWQnhJSURwSzU2djBYWF8zSHhtekVfTWh6QlBxVV9oUHpKZlNuR092N1dkUVgw?oc=5</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
